--- a/kebenajobs_tracker.xlsx
+++ b/kebenajobs_tracker.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,6 +600,25 @@
         <v>1</v>
       </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-10-02 16:57:30 UTC</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/kebenajobs_tracker.xlsx
+++ b/kebenajobs_tracker.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,6 +619,25 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-03 10:53:21 UTC</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
         <v>0</v>
       </c>
     </row>
